--- a/Documents/SCI_SE_9.ProjectTestReport.xlsx
+++ b/Documents/SCI_SE_9.ProjectTestReport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="TestReportSprint1" sheetId="3" r:id="rId1"/>
@@ -114,10 +114,10 @@
     <t>Kiểm tra chức năng quên mật khẩu</t>
   </si>
   <si>
-    <t>Lấy lại mật khẩu</t>
+    <t>Đặt lại mật khẩu</t>
   </si>
   <si>
-    <t>Kiểm tra chức năng lấy lại mật khẩu</t>
+    <t>Kiểm tra chức năng đặt lại mật khẩu</t>
   </si>
   <si>
     <t>Danh sách việc làm</t>

--- a/Documents/SCI_SE_9.ProjectTestReport.xlsx
+++ b/Documents/SCI_SE_9.ProjectTestReport.xlsx
@@ -2120,7 +2120,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="15">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="D8" s="44"/>
       <c r="E8" s="39"/>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C10" s="46">
         <f>SUM(C8,C9)</f>
-        <v>1291</v>
+        <v>1297</v>
       </c>
       <c r="D10" s="44"/>
       <c r="E10" s="39"/>
@@ -2348,7 +2348,7 @@
       <c r="B15" s="49"/>
       <c r="C15" s="46">
         <f>SUM(C10,C14)</f>
-        <v>2582</v>
+        <v>2588</v>
       </c>
       <c r="D15" s="44"/>
       <c r="E15" s="39"/>
@@ -31129,7 +31129,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="15">
-        <v>1522</v>
+        <v>1526</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="7"/>
@@ -31194,7 +31194,7 @@
       </c>
       <c r="C10" s="18">
         <f>SUM(C8,C9)</f>
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="7"/>
@@ -31324,7 +31324,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="18">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="7"/>
@@ -31357,7 +31357,7 @@
       <c r="B15" s="21"/>
       <c r="C15" s="18">
         <f>SUM(C10,C14)</f>
-        <v>3055</v>
+        <v>3057</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="7"/>
